--- a/data/trans_dic/P20B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 56,3</t>
+          <t>11,55; 56,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 47,47</t>
+          <t>18,3; 47,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,38; 66,95</t>
+          <t>34,82; 66,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,57; 51,18</t>
+          <t>25,11; 52,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,19; 37,47</t>
+          <t>13,27; 38,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 37,02</t>
+          <t>16,19; 36,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 44,74</t>
+          <t>17,43; 46,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 40,17</t>
+          <t>16,97; 42,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 36,95</t>
+          <t>16,79; 37,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,34; 36,64</t>
+          <t>20,75; 36,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,3; 49,67</t>
+          <t>28,63; 50,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 41,76</t>
+          <t>22,73; 42,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 36,45</t>
+          <t>10,06; 35,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 38,28</t>
+          <t>14,34; 38,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 41,46</t>
+          <t>14,29; 40,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 39,79</t>
+          <t>14,72; 38,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 22,11</t>
+          <t>6,72; 23,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 37,77</t>
+          <t>18,82; 37,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 31,23</t>
+          <t>11,82; 30,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 34,2</t>
+          <t>13,48; 38,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 23,82</t>
+          <t>9,75; 23,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,87; 35,39</t>
+          <t>20,45; 35,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,23; 31,05</t>
+          <t>15,86; 30,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 32,76</t>
+          <t>16,66; 33,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 39,62</t>
+          <t>10,61; 37,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 52,33</t>
+          <t>20,76; 52,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 54,4</t>
+          <t>18,19; 55,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,28; 55,98</t>
+          <t>24,75; 57,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,45; 42,13</t>
+          <t>18,2; 42,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 34,83</t>
+          <t>14,03; 34,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,17; 38,56</t>
+          <t>13,83; 38,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 30,52</t>
+          <t>9,61; 29,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 36,71</t>
+          <t>18,12; 35,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 37,85</t>
+          <t>18,94; 37,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,27; 38,56</t>
+          <t>19,21; 38,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 39,85</t>
+          <t>19,16; 39,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,57; 46,0</t>
+          <t>18,79; 46,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 42,27</t>
+          <t>17,38; 42,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 42,22</t>
+          <t>15,58; 40,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 43,39</t>
+          <t>22,89; 44,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 29,94</t>
+          <t>9,49; 27,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 30,31</t>
+          <t>13,82; 31,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 35,48</t>
+          <t>15,82; 34,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,89; 33,54</t>
+          <t>16,57; 32,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 30,34</t>
+          <t>15,83; 30,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,6; 32,22</t>
+          <t>17,38; 31,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 34,68</t>
+          <t>18,04; 34,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 35,33</t>
+          <t>21,34; 34,61</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,86; 34,1</t>
+          <t>19,5; 34,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,14; 37,79</t>
+          <t>23,73; 37,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,84</t>
+          <t>25,74; 41,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,4; 39,67</t>
+          <t>26,82; 39,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,34</t>
+          <t>14,8; 25,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 29,43</t>
+          <t>19,95; 29,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,62</t>
+          <t>18,85; 30,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,91</t>
+          <t>18,49; 28,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,69</t>
+          <t>18,71; 26,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 30,62</t>
+          <t>22,6; 30,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 32,62</t>
+          <t>23,71; 32,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,49; 31,91</t>
+          <t>23,75; 32,09</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2784; 9716</t>
+          <t>1994; 9705</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8437; 21547</t>
+          <t>8307; 21599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12746; 24117</t>
+          <t>12545; 24107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10454; 22700</t>
+          <t>11138; 23393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6220; 17665</t>
+          <t>6257; 17930</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12110; 27574</t>
+          <t>12057; 27105</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7910; 20643</t>
+          <t>8041; 21433</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7352; 16951</t>
+          <t>7160; 17757</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10795; 23799</t>
+          <t>10811; 24254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24388; 43920</t>
+          <t>24872; 43582</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23253; 40816</t>
+          <t>23524; 41609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19926; 36146</t>
+          <t>19671; 36580</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3872; 13588</t>
+          <t>3750; 13059</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9466; 23571</t>
+          <t>8829; 23860</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7031; 18937</t>
+          <t>6529; 18556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6623; 18895</t>
+          <t>6992; 18401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5051; 16654</t>
+          <t>5063; 17350</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17688; 36383</t>
+          <t>18132; 36476</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9406; 24046</t>
+          <t>9104; 23716</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7972; 21667</t>
+          <t>8543; 24658</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11109; 26815</t>
+          <t>10973; 26544</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31380; 55882</t>
+          <t>32287; 55360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18684; 38090</t>
+          <t>19455; 37612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17872; 36316</t>
+          <t>18467; 36614</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3939; 15001</t>
+          <t>4017; 14156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9881; 24969</t>
+          <t>9905; 25199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5998; 18058</t>
+          <t>6038; 18586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8238; 19810</t>
+          <t>8757; 20301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11212; 24283</t>
+          <t>10489; 24429</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10491; 26280</t>
+          <t>10585; 26216</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7913; 21534</t>
+          <t>7725; 21743</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3821; 11850</t>
+          <t>3732; 11345</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18082; 35054</t>
+          <t>17302; 33929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24100; 46620</t>
+          <t>23334; 46098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17159; 34329</t>
+          <t>17100; 34655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14294; 29573</t>
+          <t>14220; 29076</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7721; 19124</t>
+          <t>7815; 19244</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8843; 22442</t>
+          <t>9228; 22397</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7764; 20089</t>
+          <t>7412; 19284</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13837; 26394</t>
+          <t>13925; 27015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6348; 20443</t>
+          <t>6482; 19025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11876; 26750</t>
+          <t>12198; 27699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13926; 32123</t>
+          <t>14327; 31335</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12237; 24303</t>
+          <t>12006; 23585</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17091; 33326</t>
+          <t>17392; 33912</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24878; 45539</t>
+          <t>24562; 45032</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25825; 47900</t>
+          <t>24911; 47025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28710; 47093</t>
+          <t>28446; 46140</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25274; 45688</t>
+          <t>26122; 45854</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48081; 78523</t>
+          <t>49306; 78396</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42502; 66360</t>
+          <t>41819; 67203</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49639; 74594</t>
+          <t>50441; 74818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38941; 62932</t>
+          <t>36755; 62079</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66124; 98443</t>
+          <t>66734; 98841</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51703; 79847</t>
+          <t>50800; 81415</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39667; 60527</t>
+          <t>40092; 61718</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69951; 102057</t>
+          <t>71546; 102438</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125411; 166042</t>
+          <t>122540; 167472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101246; 140920</t>
+          <t>102423; 142450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95101; 129204</t>
+          <t>96172; 129947</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,55; 56,24</t>
+          <t>11,49; 56,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 47,59</t>
+          <t>20,89; 48,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,82; 66,92</t>
+          <t>33,45; 66,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 52,75</t>
+          <t>22,82; 49,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 38,03</t>
+          <t>13,11; 38,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 36,39</t>
+          <t>16,34; 36,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,43; 46,45</t>
+          <t>17,25; 45,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 42,08</t>
+          <t>18,26; 41,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 37,66</t>
+          <t>17,07; 37,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,75; 36,36</t>
+          <t>20,15; 36,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,63; 50,64</t>
+          <t>28,03; 49,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,73; 42,27</t>
+          <t>23,37; 41,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,06; 35,03</t>
+          <t>10,06; 37,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 38,75</t>
+          <t>15,19; 37,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 40,62</t>
+          <t>14,82; 42,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 38,75</t>
+          <t>17,45; 45,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 23,04</t>
+          <t>7,14; 24,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,82; 37,87</t>
+          <t>18,52; 37,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 30,8</t>
+          <t>11,16; 31,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 38,92</t>
+          <t>13,96; 36,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 23,57</t>
+          <t>9,91; 23,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,45; 35,06</t>
+          <t>20,02; 35,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 30,66</t>
+          <t>15,63; 32,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 33,03</t>
+          <t>17,76; 35,52</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 37,39</t>
+          <t>10,75; 39,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 52,81</t>
+          <t>19,76; 50,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 55,99</t>
+          <t>18,31; 56,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 57,36</t>
+          <t>25,11; 58,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,2; 42,38</t>
+          <t>19,12; 42,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,03; 34,74</t>
+          <t>13,9; 33,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 38,94</t>
+          <t>14,14; 38,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 29,22</t>
+          <t>10,7; 28,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 35,53</t>
+          <t>17,59; 36,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,94; 37,43</t>
+          <t>18,77; 35,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 38,92</t>
+          <t>18,48; 39,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,16; 39,18</t>
+          <t>19,63; 38,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 46,28</t>
+          <t>18,65; 44,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 42,19</t>
+          <t>16,64; 40,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 40,53</t>
+          <t>16,99; 42,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,89; 44,41</t>
+          <t>22,05; 43,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 27,86</t>
+          <t>10,11; 30,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 31,38</t>
+          <t>13,99; 31,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,82; 34,61</t>
+          <t>15,15; 35,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 32,55</t>
+          <t>17,02; 32,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 30,87</t>
+          <t>15,93; 32,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 31,86</t>
+          <t>17,95; 32,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,04; 34,05</t>
+          <t>18,3; 34,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,34; 34,61</t>
+          <t>21,88; 33,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,75; 33,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,73; 37,73</t>
+          <t>23,42; 37,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,36</t>
+          <t>26,65; 42,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,82; 39,78</t>
+          <t>26,74; 39,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,0</t>
+          <t>15,55; 25,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,55</t>
+          <t>20,11; 29,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,21</t>
+          <t>19,59; 30,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,46</t>
+          <t>18,47; 29,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,79</t>
+          <t>18,4; 26,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,6; 30,88</t>
+          <t>23,22; 30,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,97</t>
+          <t>23,57; 32,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,75; 32,09</t>
+          <t>24,16; 32,08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15997</t>
+          <t>16651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>29970</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1994; 9705</t>
+          <t>1984; 9676</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8307; 21599</t>
+          <t>9480; 21919</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12545; 24107</t>
+          <t>12050; 23775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11138; 23393</t>
+          <t>10937; 23726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6257; 17930</t>
+          <t>6183; 18136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12057; 27105</t>
+          <t>12171; 27315</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8041; 21433</t>
+          <t>7959; 20836</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7160; 17757</t>
+          <t>8562; 19452</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10811; 24254</t>
+          <t>10993; 24109</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24872; 43582</t>
+          <t>24153; 43155</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23524; 41609</t>
+          <t>23030; 40972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19671; 36580</t>
+          <t>22160; 39562</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>31105</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3750; 13059</t>
+          <t>3749; 13939</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8829; 23860</t>
+          <t>9356; 23387</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6529; 18556</t>
+          <t>6771; 19208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6992; 18401</t>
+          <t>9529; 24640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5063; 17350</t>
+          <t>5376; 18333</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18132; 36476</t>
+          <t>17841; 36323</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9104; 23716</t>
+          <t>8595; 23906</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8543; 24658</t>
+          <t>9734; 25326</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10973; 26544</t>
+          <t>11161; 26822</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32287; 55360</t>
+          <t>31609; 55416</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19455; 37612</t>
+          <t>19172; 39659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18467; 36614</t>
+          <t>22081; 44166</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>24635</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4017; 14156</t>
+          <t>4069; 15073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9905; 25199</t>
+          <t>9427; 24120</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6038; 18586</t>
+          <t>6077; 18770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8757; 20301</t>
+          <t>9554; 22170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10489; 24429</t>
+          <t>11019; 24417</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10585; 26216</t>
+          <t>10488; 25626</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7725; 21743</t>
+          <t>7898; 21293</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3732; 11345</t>
+          <t>5325; 14187</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17302; 33929</t>
+          <t>16795; 34600</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23334; 46098</t>
+          <t>23124; 43869</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17100; 34655</t>
+          <t>16455; 35281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14220; 29076</t>
+          <t>17234; 33877</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>39777</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7815; 19244</t>
+          <t>7753; 18663</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9228; 22397</t>
+          <t>8836; 21689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7412; 19284</t>
+          <t>8083; 20162</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13925; 27015</t>
+          <t>14242; 27789</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6482; 19025</t>
+          <t>6904; 20529</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12198; 27699</t>
+          <t>12349; 27524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14327; 31335</t>
+          <t>13716; 31701</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12006; 23585</t>
+          <t>13462; 25783</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17392; 33912</t>
+          <t>17505; 35248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24562; 45032</t>
+          <t>25370; 46409</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24911; 47025</t>
+          <t>25276; 47028</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28446; 46140</t>
+          <t>31447; 48729</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26122; 45854</t>
+          <t>26457; 45426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49306; 78396</t>
+          <t>48660; 77457</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41819; 67203</t>
+          <t>43294; 68491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50441; 74818</t>
+          <t>54867; 81090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36755; 62079</t>
+          <t>38624; 63528</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66734; 98841</t>
+          <t>67275; 99595</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50800; 81415</t>
+          <t>52809; 81571</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40092; 61718</t>
+          <t>45331; 71653</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71546; 102438</t>
+          <t>70362; 102503</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>122540; 167472</t>
+          <t>125932; 166310</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102423; 142450</t>
+          <t>101805; 140282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96172; 129947</t>
+          <t>108858; 144554</t>
         </is>
       </c>
     </row>
